--- a/Stock_Data.xlsx
+++ b/Stock_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\New Capstone Project\Stock Market Project\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E3AC8FD-C87D-46CD-90BD-013B35988F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="dim_exchange" sheetId="1" r:id="rId1"/>
@@ -5595,7 +5594,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5640,7 +5639,224 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5651,6 +5867,195 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table12" displayName="Table12" ref="A1:D3" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="exchange_id"/>
+    <tableColumn id="2" name="exchange_name"/>
+    <tableColumn id="3" name="country"/>
+    <tableColumn id="4" name="currency"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:N501" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:N501"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="order_id"/>
+    <tableColumn id="2" name="order_ts"/>
+    <tableColumn id="3" name="company_id"/>
+    <tableColumn id="4" name="side"/>
+    <tableColumn id="5" name="quantity"/>
+    <tableColumn id="6" name="status"/>
+    <tableColumn id="7" name="order_type"/>
+    <tableColumn id="8" name="trader_id"/>
+    <tableColumn id="9" name="portfolio_id"/>
+    <tableColumn id="10" name="date"/>
+    <tableColumn id="11" name="calendar_id"/>
+    <tableColumn id="12" name="order_ts_imputed"/>
+    <tableColumn id="13" name="limit_price_imputed"/>
+    <tableColumn id="14" name="portfolio_id_imputed"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:P501" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:P501"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="trade_id"/>
+    <tableColumn id="2" name="order_id"/>
+    <tableColumn id="3" name="trade_ts"/>
+    <tableColumn id="4" name="company_id"/>
+    <tableColumn id="5" name="side"/>
+    <tableColumn id="6" name="quantity"/>
+    <tableColumn id="7" name="price"/>
+    <tableColumn id="8" name="fees"/>
+    <tableColumn id="9" name="trader_id"/>
+    <tableColumn id="10" name="portfolio_id"/>
+    <tableColumn id="11" name="date"/>
+    <tableColumn id="12" name="calendar_id"/>
+    <tableColumn id="13" name="trade_ts_imputed"/>
+    <tableColumn id="14" name="fees_imputed"/>
+    <tableColumn id="15" name="portfolio_id_imputed"/>
+    <tableColumn id="16" name="is_orphan_trade"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:E11"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="portfolio_id"/>
+    <tableColumn id="2" name="company_id"/>
+    <tableColumn id="3" name="date"/>
+    <tableColumn id="4" name="quantity"/>
+    <tableColumn id="5" name="calendar_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table11" displayName="Table11" ref="A1:B6" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:B6"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="sector_id"/>
+    <tableColumn id="2" name="sector_name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table10" displayName="Table10" ref="A1:E9" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:E9"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="company_id"/>
+    <tableColumn id="2" name="ticker"/>
+    <tableColumn id="3" name="company_name"/>
+    <tableColumn id="4" name="sector_id"/>
+    <tableColumn id="5" name="exchange_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table9" displayName="Table9" ref="A1:C31" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:C31"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="trader_id"/>
+    <tableColumn id="2" name="trader_name"/>
+    <tableColumn id="3" name="desk"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C11" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:C11"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="portfolio_id"/>
+    <tableColumn id="2" name="portfolio_name"/>
+    <tableColumn id="3" name="manager"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:F182" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:F182"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="date"/>
+    <tableColumn id="2" name="calendar_id"/>
+    <tableColumn id="3" name="year"/>
+    <tableColumn id="4" name="month"/>
+    <tableColumn id="5" name="day"/>
+    <tableColumn id="6" name="is_month_start"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:L1033" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:L1033"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="date"/>
+    <tableColumn id="2" name="company_id"/>
+    <tableColumn id="3" name="open"/>
+    <tableColumn id="4" name="high"/>
+    <tableColumn id="5" name="low"/>
+    <tableColumn id="6" name="close"/>
+    <tableColumn id="7" name="volume"/>
+    <tableColumn id="8" name="calendar_id"/>
+    <tableColumn id="9" name="cumulative_factor"/>
+    <tableColumn id="10" name="adjusted_close"/>
+    <tableColumn id="11" name="avg_vol"/>
+    <tableColumn id="12" name="is_volume_suspect"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:F9" totalsRowShown="0" headerRowDxfId="7">
+  <autoFilter ref="A1:F9"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="date"/>
+    <tableColumn id="2" name="company_id"/>
+    <tableColumn id="3" name="dividend_per_share"/>
+    <tableColumn id="4" name="calendar_id"/>
+    <tableColumn id="5" name="exchange_id"/>
+    <tableColumn id="6" name="is_orphan_dividend"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A1:E6"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="company_id"/>
+    <tableColumn id="2" name="date"/>
+    <tableColumn id="3" name="split_ratio"/>
+    <tableColumn id="4" name="calendar_id"/>
+    <tableColumn id="5" name="exchange_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5937,14 +6342,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5991,28 +6396,31 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28061,29 +28469,32 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
     <col min="7" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" customWidth="1"/>
+    <col min="15" max="15" width="22.28515625" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -53138,19 +53549,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -53342,14 +53756,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -53403,18 +53821,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -53572,11 +53994,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -53928,16 +54353,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -54064,20 +54492,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -57722,23 +58153,26 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L1033"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -96997,20 +97431,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -97195,19 +97632,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -97314,5 +97754,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>